--- a/hira_material_automation/output/monthly/202601_202609__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__temporary_synovial_substitute__250099__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04T22:53:39</t>
+          <t>2026-09-14T23:45:18</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20753cb692d3a67ebdb8bd08c36b2c30791f8960500676ad87bd1dd48bb73c41</t>
+          <t>12ba564da139f35893303b1fbad29a143c5bbdbfbcb3cedc7421560f200c7862</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202609__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__temporary_synovial_substitute__250099__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14T23:45:18</t>
+          <t>2026-09-24T23:48:38</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12ba564da139f35893303b1fbad29a143c5bbdbfbcb3cedc7421560f200c7862</t>
+          <t>610f4ccc0a167affbe29e7e6e50cad9be312d5dbcacf52e9339342e874c661ce</t>
         </is>
       </c>
     </row>
